--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.93678639537137</v>
+        <v>10.87722778924785</v>
       </c>
       <c r="D2" t="n">
-        <v>66.85755911656877</v>
+        <v>10.86435335644243</v>
       </c>
       <c r="E2" t="n">
-        <v>14.90141496070302</v>
+        <v>2.421479931114241</v>
       </c>
       <c r="F2" t="n">
-        <v>18.86208669721328</v>
+        <v>3.065089088297158</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.65367165668071</v>
+        <v>8.881221644210616</v>
       </c>
       <c r="D3" t="n">
-        <v>54.54693329916974</v>
+        <v>8.863876661115084</v>
       </c>
       <c r="E3" t="n">
-        <v>14.90141496070302</v>
+        <v>2.421479931114241</v>
       </c>
       <c r="F3" t="n">
-        <v>18.86208669721328</v>
+        <v>3.065089088297158</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>68.44189065715457</v>
+        <v>11.12180723178762</v>
       </c>
       <c r="D4" t="n">
-        <v>68.52003198385275</v>
+        <v>11.13450519737607</v>
       </c>
       <c r="E4" t="n">
-        <v>14.90141496070302</v>
+        <v>2.421479931114241</v>
       </c>
       <c r="F4" t="n">
-        <v>18.86208669721328</v>
+        <v>3.065089088297158</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.54923382677655</v>
+        <v>5.12675049685119</v>
       </c>
       <c r="D5" t="n">
-        <v>31.41859101278004</v>
+        <v>5.105521039576757</v>
       </c>
       <c r="E5" t="n">
-        <v>14.90141496070302</v>
+        <v>2.421479931114241</v>
       </c>
       <c r="F5" t="n">
-        <v>18.86208669721328</v>
+        <v>3.065089088297158</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.36518593056335</v>
+        <v>5.584342713716545</v>
       </c>
       <c r="D6" t="n">
-        <v>12.37941840313995</v>
+        <v>2.011655490510242</v>
       </c>
       <c r="E6" t="n">
-        <v>14.90141496070302</v>
+        <v>2.421479931114241</v>
       </c>
       <c r="F6" t="n">
-        <v>18.86208669721328</v>
+        <v>3.065089088297158</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.19235115237905</v>
+        <v>3.931257062261596</v>
       </c>
       <c r="D7" t="n">
-        <v>23.99257451293038</v>
+        <v>3.898793358351187</v>
       </c>
       <c r="E7" t="n">
-        <v>14.90141496070302</v>
+        <v>2.421479931114241</v>
       </c>
       <c r="F7" t="n">
-        <v>18.86208669721328</v>
+        <v>3.065089088297158</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.03924697857052</v>
+        <v>6.506377634017709</v>
       </c>
       <c r="D8" t="n">
-        <v>17.11724276862369</v>
+        <v>2.78155194990135</v>
       </c>
       <c r="E8" t="n">
-        <v>14.90141496070302</v>
+        <v>2.421479931114241</v>
       </c>
       <c r="F8" t="n">
-        <v>18.86208669721328</v>
+        <v>3.065089088297158</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.91207379256995</v>
+        <v>6.323211991292617</v>
       </c>
       <c r="D9" t="n">
-        <v>25.60152604469407</v>
+        <v>4.160247982262786</v>
       </c>
       <c r="E9" t="n">
-        <v>14.90141496070302</v>
+        <v>2.421479931114241</v>
       </c>
       <c r="F9" t="n">
-        <v>18.86208669721328</v>
+        <v>3.065089088297158</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.61624927892763</v>
+        <v>4.975140507825739</v>
       </c>
       <c r="D10" t="n">
-        <v>30.6185770531817</v>
+        <v>4.975518771142026</v>
       </c>
       <c r="E10" t="n">
-        <v>14.90141496070302</v>
+        <v>2.421479931114241</v>
       </c>
       <c r="F10" t="n">
-        <v>18.86208669721328</v>
+        <v>3.065089088297158</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>52.30382715825074</v>
+        <v>8.499371913215745</v>
       </c>
       <c r="D11" t="n">
-        <v>52.4630062490864</v>
+        <v>8.525238515476541</v>
       </c>
       <c r="E11" t="n">
-        <v>14.90141496070302</v>
+        <v>2.421479931114241</v>
       </c>
       <c r="F11" t="n">
-        <v>18.86208669721328</v>
+        <v>3.065089088297158</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>55.82345648612293</v>
+        <v>9.071311678994975</v>
       </c>
       <c r="D12" t="n">
-        <v>55.88709437671129</v>
+        <v>9.081652836215584</v>
       </c>
       <c r="E12" t="n">
-        <v>14.90141496070302</v>
+        <v>2.421479931114241</v>
       </c>
       <c r="F12" t="n">
-        <v>18.86208669721328</v>
+        <v>3.065089088297158</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.02139291594273</v>
+        <v>4.065976348840694</v>
       </c>
       <c r="D13" t="n">
-        <v>25.04274806316343</v>
+        <v>4.069446560264057</v>
       </c>
       <c r="E13" t="n">
-        <v>14.90141496070302</v>
+        <v>2.421479931114241</v>
       </c>
       <c r="F13" t="n">
-        <v>18.86208669721328</v>
+        <v>3.065089088297158</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
